--- a/heat_utilities_summary.xlsx
+++ b/heat_utilities_summary.xlsx
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>636790610.8416338</v>
+        <v>636790610.8346858</v>
       </c>
       <c r="D2" t="n">
-        <v>3.795543069328626</v>
+        <v>3.795535741418837</v>
       </c>
     </row>
     <row r="3">
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>321566472.486055</v>
+        <v>321568632.5927471</v>
       </c>
       <c r="D3" t="n">
-        <v>1.916673040074764</v>
+        <v>1.916682214778774</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>23009674.4457905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1371474529984043</v>
+        <v>0.1371471882145603</v>
       </c>
     </row>
     <row r="5">
@@ -516,10 +516,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9443493.674829477</v>
+        <v>9443493.67479853</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05628724161051071</v>
+        <v>0.05628713293931652</v>
       </c>
     </row>
     <row r="6">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2357798.901048638</v>
+        <v>2357798.904343389</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01405348496881561</v>
+        <v>0.01405345785608127</v>
       </c>
     </row>
     <row r="7">
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6181.701378594263</v>
+        <v>6181.701378594211</v>
       </c>
       <c r="D7" t="n">
-        <v>3.684557125170578e-05</v>
+        <v>3.684550011577276e-05</v>
       </c>
     </row>
     <row r="8">
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2359210.176080855</v>
+        <v>-2359210.176080748</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.01406189676866983</v>
+        <v>-0.01406186962005653</v>
       </c>
     </row>
     <row r="9">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-9608932.041592725</v>
+        <v>-9608932.053399816</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.05727332468974985</v>
+        <v>-0.05727321418533316</v>
       </c>
     </row>
     <row r="10">
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-27509096.36424643</v>
+        <v>-27509096.36516958</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1639659226614688</v>
+        <v>-0.1639656061060266</v>
       </c>
     </row>
     <row r="11">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-272413434.8599544</v>
+        <v>-272413434.9551353</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.623700015469989</v>
+        <v>-1.623696881239525</v>
       </c>
     </row>
     <row r="12">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-513510304.7660928</v>
+        <v>-513512140.8489923</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.060739974962495</v>
+        <v>-3.060745009556742</v>
       </c>
     </row>
   </sheetData>
